--- a/SGC-CKN/Excel/95872ff4-d067-466f-a3c2-5b3f6c2e8ab8_Thi_công_cọc_khoan_nhồi_đại_trà_P7-78_D800_06-03-2026.xlsx
+++ b/SGC-CKN/Excel/95872ff4-d067-466f-a3c2-5b3f6c2e8ab8_Thi_công_cọc_khoan_nhồi_đại_trà_P7-78_D800_06-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
   <si>
     <t>Dự án</t>
   </si>
@@ -98,11 +98,11 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">09:35
+    <t xml:space="preserve">18:35
 05/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">11:42
+    <t xml:space="preserve">18:42
 05/03/2026</t>
   </si>
   <si>
@@ -144,11 +144,11 @@
   </si>
   <si>
     <t xml:space="preserve">13:00
-05/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00
-05/03/2026</t>
+06/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:25
+06/03/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -157,12 +157,12 @@
     <t>Cát thô vừa, vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">14:28
-05/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:46
-05/03/2026</t>
+    <t xml:space="preserve">14:26
+06/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:46
+06/03/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -171,12 +171,12 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">16:48
-05/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:20
-05/03/2026</t>
+    <t xml:space="preserve">16:47
+06/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:10
+06/03/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -186,11 +186,11 @@
   </si>
   <si>
     <t xml:space="preserve">18:11
-05/03/2026</t>
+06/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">18:59
-05/03/2026</t>
+06/03/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -199,33 +199,37 @@
     <t>Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
+    <t xml:space="preserve">19:00
+06/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:10
+06/03/2026</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:11
+06/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:39
+06/03/2026</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Cuội đa màu sắc TT rất chặt</t>
+  </si>
+  <si>
     <t xml:space="preserve">19:20
-05/03/2026</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:24
-05/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:39
-05/03/2026</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:40
-05/03/2026</t>
+06/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">19:50
-05/03/2026</t>
+06/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -384,7 +388,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -394,12 +398,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA7F3D0"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -565,17 +569,17 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1235,16 +1239,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-6.19</v>
+        <v>-6.94</v>
       </c>
       <c r="H11" s="5">
-        <v>2.12</v>
+        <v>0.12</v>
       </c>
       <c r="I11" s="5">
-        <v>6.19</v>
+        <v>6.94</v>
       </c>
       <c r="J11" s="8">
-        <v>2.92</v>
+        <v>59.49</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1267,7 +1271,7 @@
         <v>34</v>
       </c>
       <c r="F12" s="9">
-        <v>-6.19</v>
+        <v>-6.94</v>
       </c>
       <c r="G12" s="9">
         <v>-9.04</v>
@@ -1276,47 +1280,47 @@
         <v>0.28</v>
       </c>
       <c r="I12" s="9">
-        <v>2.85</v>
-      </c>
-      <c r="J12" s="12">
-        <v>10.06</v>
+        <v>2.1</v>
+      </c>
+      <c r="J12" s="8">
+        <v>7.41</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>-9.04</v>
       </c>
-      <c r="G13" s="13">
-        <v>-12.24</v>
-      </c>
-      <c r="H13" s="13">
+      <c r="G13" s="12">
+        <v>-17.24</v>
+      </c>
+      <c r="H13" s="12">
         <v>2.98</v>
       </c>
-      <c r="I13" s="13">
-        <v>3.2</v>
-      </c>
-      <c r="J13" s="8">
-        <v>1.07</v>
-      </c>
-      <c r="K13" s="14" t="s">
+      <c r="I13" s="12">
+        <v>8.2</v>
+      </c>
+      <c r="J13" s="15">
+        <v>2.75</v>
+      </c>
+      <c r="K13" s="13" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1337,19 +1341,19 @@
         <v>42</v>
       </c>
       <c r="F14" s="16">
-        <v>-12.24</v>
+        <v>-17.24</v>
       </c>
       <c r="G14" s="16">
         <v>-21.54</v>
       </c>
       <c r="H14" s="16">
-        <v>1</v>
+        <v>1.42</v>
       </c>
       <c r="I14" s="16">
-        <v>9.3</v>
-      </c>
-      <c r="J14" s="12">
-        <v>9.3</v>
+        <v>4.3</v>
+      </c>
+      <c r="J14" s="15">
+        <v>3.04</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1378,13 +1382,13 @@
         <v>-25.54</v>
       </c>
       <c r="H15" s="19">
-        <v>1.3</v>
+        <v>2.33</v>
       </c>
       <c r="I15" s="19">
         <v>4</v>
       </c>
-      <c r="J15" s="8">
-        <v>3.08</v>
+      <c r="J15" s="15">
+        <v>1.71</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1413,13 +1417,13 @@
         <v>-35.64</v>
       </c>
       <c r="H16" s="22">
-        <v>0.53</v>
+        <v>1.38</v>
       </c>
       <c r="I16" s="22">
         <v>10.1</v>
       </c>
-      <c r="J16" s="12">
-        <v>18.94</v>
+      <c r="J16" s="8">
+        <v>7.3</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1445,16 +1449,16 @@
         <v>-35.64</v>
       </c>
       <c r="G17" s="25">
-        <v>-38.05</v>
+        <v>-37.05</v>
       </c>
       <c r="H17" s="25">
         <v>0.8</v>
       </c>
       <c r="I17" s="25">
-        <v>2.41</v>
-      </c>
-      <c r="J17" s="8">
-        <v>3.01</v>
+        <v>1.41</v>
+      </c>
+      <c r="J17" s="15">
+        <v>1.76</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1471,25 +1475,25 @@
         <v>56</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F18" s="28">
-        <v>-38.05</v>
+        <v>-37.05</v>
       </c>
       <c r="G18" s="28">
         <v>-39.5</v>
       </c>
       <c r="H18" s="28">
-        <v>0.33</v>
+        <v>0.17</v>
       </c>
       <c r="I18" s="28">
-        <v>1.45</v>
+        <v>2.45</v>
       </c>
       <c r="J18" s="8">
-        <v>4.35</v>
+        <v>14.7</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1497,7 +1501,7 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
@@ -1506,25 +1510,25 @@
         <v>52</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F19" s="31">
         <v>-39.5</v>
       </c>
       <c r="G19" s="31">
-        <v>-44.25</v>
+        <v>-44.15</v>
       </c>
       <c r="H19" s="31">
-        <v>0.25</v>
+        <v>0.47</v>
       </c>
       <c r="I19" s="31">
-        <v>4.75</v>
-      </c>
-      <c r="J19" s="12">
-        <v>19</v>
+        <v>4.65</v>
+      </c>
+      <c r="J19" s="8">
+        <v>9.96</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>30</v>
@@ -1532,34 +1536,34 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F20" s="34">
-        <v>-44.25</v>
+        <v>-44.15</v>
       </c>
       <c r="G20" s="34">
-        <v>-45.9</v>
+        <v>-45.33</v>
       </c>
       <c r="H20" s="34">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="I20" s="34">
-        <v>1.65</v>
-      </c>
-      <c r="J20" s="12">
-        <v>9.9</v>
+        <v>1.18</v>
+      </c>
+      <c r="J20" s="15">
+        <v>2.36</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
@@ -1567,7 +1571,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1673,31 +1677,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1717,16 +1721,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-6.19</v>
+        <v>-6.94</v>
       </c>
       <c r="G2" s="5">
-        <v>2.12</v>
+        <v>0.12</v>
       </c>
       <c r="H2" s="5">
-        <v>6.19</v>
+        <v>6.94</v>
       </c>
       <c r="I2" s="8">
-        <v>2.92</v>
+        <v>59.49</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1743,7 +1747,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-6.19</v>
+        <v>-6.94</v>
       </c>
       <c r="F3" s="9">
         <v>-9.04</v>
@@ -1752,39 +1756,39 @@
         <v>0.28</v>
       </c>
       <c r="H3" s="9">
-        <v>2.85</v>
-      </c>
-      <c r="I3" s="12">
-        <v>10.06</v>
+        <v>2.1</v>
+      </c>
+      <c r="I3" s="8">
+        <v>7.41</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>-9.04</v>
       </c>
-      <c r="F4" s="13">
-        <v>-12.24</v>
-      </c>
-      <c r="G4" s="13">
+      <c r="F4" s="12">
+        <v>-17.24</v>
+      </c>
+      <c r="G4" s="12">
         <v>2.98</v>
       </c>
-      <c r="H4" s="13">
-        <v>3.2</v>
-      </c>
-      <c r="I4" s="8">
-        <v>1.07</v>
+      <c r="H4" s="12">
+        <v>8.2</v>
+      </c>
+      <c r="I4" s="15">
+        <v>2.75</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1801,19 +1805,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>-12.24</v>
+        <v>-17.24</v>
       </c>
       <c r="F5" s="16">
         <v>-21.54</v>
       </c>
       <c r="G5" s="16">
-        <v>1</v>
+        <v>1.42</v>
       </c>
       <c r="H5" s="16">
-        <v>9.3</v>
-      </c>
-      <c r="I5" s="12">
-        <v>9.3</v>
+        <v>4.3</v>
+      </c>
+      <c r="I5" s="15">
+        <v>3.04</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1836,13 +1840,13 @@
         <v>-25.54</v>
       </c>
       <c r="G6" s="19">
-        <v>1.3</v>
+        <v>2.33</v>
       </c>
       <c r="H6" s="19">
         <v>4</v>
       </c>
-      <c r="I6" s="8">
-        <v>3.08</v>
+      <c r="I6" s="15">
+        <v>1.71</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1865,13 +1869,13 @@
         <v>-35.64</v>
       </c>
       <c r="G7" s="22">
-        <v>0.53</v>
+        <v>1.38</v>
       </c>
       <c r="H7" s="22">
         <v>10.1</v>
       </c>
-      <c r="I7" s="12">
-        <v>18.94</v>
+      <c r="I7" s="8">
+        <v>7.3</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1891,16 +1895,16 @@
         <v>-35.64</v>
       </c>
       <c r="F8" s="25">
-        <v>-38.05</v>
+        <v>-37.05</v>
       </c>
       <c r="G8" s="25">
         <v>0.8</v>
       </c>
       <c r="H8" s="25">
-        <v>2.41</v>
-      </c>
-      <c r="I8" s="8">
-        <v>3.01</v>
+        <v>1.41</v>
+      </c>
+      <c r="I8" s="15">
+        <v>1.76</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1917,19 +1921,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-38.05</v>
+        <v>-37.05</v>
       </c>
       <c r="F9" s="28">
         <v>-39.5</v>
       </c>
       <c r="G9" s="28">
-        <v>0.33</v>
+        <v>0.17</v>
       </c>
       <c r="H9" s="28">
-        <v>1.45</v>
+        <v>2.45</v>
       </c>
       <c r="I9" s="8">
-        <v>4.35</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1949,16 +1953,16 @@
         <v>-39.5</v>
       </c>
       <c r="F10" s="31">
-        <v>-44.25</v>
+        <v>-44.15</v>
       </c>
       <c r="G10" s="31">
-        <v>0.25</v>
+        <v>0.47</v>
       </c>
       <c r="H10" s="31">
-        <v>4.75</v>
-      </c>
-      <c r="I10" s="12">
-        <v>19</v>
+        <v>4.65</v>
+      </c>
+      <c r="I10" s="8">
+        <v>9.96</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1969,30 +1973,30 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
       </c>
       <c r="E11" s="34">
-        <v>-44.25</v>
+        <v>-44.15</v>
       </c>
       <c r="F11" s="34">
-        <v>-45.9</v>
+        <v>-45.33</v>
       </c>
       <c r="G11" s="34">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="H11" s="34">
-        <v>1.65</v>
-      </c>
-      <c r="I11" s="12">
-        <v>9.9</v>
+        <v>1.18</v>
+      </c>
+      <c r="I11" s="15">
+        <v>2.36</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
@@ -2007,16 +2011,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="39">
-        <v>-45.9</v>
+        <v>-45.33</v>
       </c>
       <c r="G12" s="39">
-        <v>9.77</v>
+        <v>10.45</v>
       </c>
       <c r="H12" s="39">
-        <v>45.9</v>
+        <v>45.33</v>
       </c>
       <c r="I12" s="39">
-        <v>4.7</v>
+        <v>4.34</v>
       </c>
     </row>
   </sheetData>
